--- a/artfynd/S 2416-2024 artfynd.xlsx
+++ b/artfynd/S 2416-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY47"/>
+  <dimension ref="A1:AZ47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -799,6 +804,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954101</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -935,6 +945,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954188</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1057,6 +1072,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713455</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1164,6 +1184,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954111</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1271,6 +1296,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954114</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1378,6 +1408,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954116</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1485,6 +1520,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954118</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1592,6 +1632,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954157</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1699,6 +1744,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954159</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1806,6 +1856,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954160</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1918,6 +1973,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954170</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2035,6 +2095,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954142</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2147,6 +2212,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954138</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2259,6 +2329,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954136</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2371,6 +2446,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954144</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2483,6 +2563,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954106</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2595,6 +2680,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954135</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2722,6 +2812,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954102</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2829,6 +2924,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954113</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2936,6 +3036,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954167</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -3063,6 +3168,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954173</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -3190,6 +3300,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954187</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3297,6 +3412,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954131</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3404,6 +3524,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954150</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3523,6 +3648,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111962068</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3635,6 +3765,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954108</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3752,6 +3887,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954120</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3878,6 +4018,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/120848742</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -4005,6 +4150,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954124</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -4132,6 +4282,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954123</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -4245,6 +4400,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954162</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -4347,6 +4507,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111891039</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4454,6 +4619,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954163</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4561,6 +4731,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954165</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4668,6 +4843,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954158</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4775,6 +4955,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954161</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4882,6 +5067,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954181</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4989,6 +5179,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111713457</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -5096,6 +5291,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954107</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -5203,6 +5403,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954134</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -5310,6 +5515,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954139</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5417,6 +5627,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954145</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5524,6 +5739,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954146</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5631,6 +5851,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954164</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5748,6 +5973,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111804210</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5859,8 +6089,61 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111954147</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>